--- a/tests/regression_artifacts/downloads/email_TSCW18489131_budget_marine_grenada/current/26609.xlsx
+++ b/tests/regression_artifacts/downloads/email_TSCW18489131_budget_marine_grenada/current/26609.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoice Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Invoice Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM16"/>
+  <dimension ref="A1:AM18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Lamps</t>
+          <t>Parts</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>85131000</t>
+          <t>94054000</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -819,7 +819,7 @@
       <c r="AJ2" s="2" t="n"/>
       <c r="AK2" s="2" t="inlineStr">
         <is>
-          <t>85131000</t>
+          <t>94054000</t>
         </is>
       </c>
       <c r="AL2" t="n">
@@ -844,12 +844,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Lamps</t>
+          <t>MARINE LIGHTING</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>85131000</t>
+          <t>94054000</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
@@ -908,7 +908,7 @@
       <c r="AJ3" s="2" t="n"/>
       <c r="AK3" s="2" t="inlineStr">
         <is>
-          <t>85131000</t>
+          <t>94054000</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       <c r="I12" s="7" t="n"/>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>CET (20%) — Tariff 85131000</t>
+          <t>CET (weighted avg 13.3%)</t>
         </is>
       </c>
       <c r="K12" s="7" t="n"/>
@@ -1250,7 +1250,7 @@
       <c r="N12" s="7" t="n"/>
       <c r="O12" s="7" t="n"/>
       <c r="P12" s="9" t="n">
-        <v>1126.74</v>
+        <v>747.39</v>
       </c>
       <c r="Q12" s="7" t="n"/>
       <c r="R12" s="7" t="n"/>
@@ -1286,7 +1286,7 @@
       <c r="I13" s="7" t="n"/>
       <c r="J13" s="8" t="inlineStr">
         <is>
-          <t>CSC (6%)</t>
+          <t xml:space="preserve">  └ 85139000: 5% CET (45% of value)</t>
         </is>
       </c>
       <c r="K13" s="7" t="n"/>
@@ -1295,7 +1295,7 @@
       <c r="N13" s="7" t="n"/>
       <c r="O13" s="7" t="n"/>
       <c r="P13" s="9" t="n">
-        <v>338.02</v>
+        <v>126.45</v>
       </c>
       <c r="Q13" s="7" t="n"/>
       <c r="R13" s="7" t="n"/>
@@ -1331,7 +1331,7 @@
       <c r="I14" s="7" t="n"/>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>VAT (15%) on CIF+CET+CSC</t>
+          <t xml:space="preserve">  └ 94054000: 20% CET (55% of value)</t>
         </is>
       </c>
       <c r="K14" s="7" t="n"/>
@@ -1340,7 +1340,7 @@
       <c r="N14" s="7" t="n"/>
       <c r="O14" s="7" t="n"/>
       <c r="P14" s="9" t="n">
-        <v>1064.77</v>
+        <v>620.9400000000001</v>
       </c>
       <c r="Q14" s="7" t="n"/>
       <c r="R14" s="7" t="n"/>
@@ -1365,49 +1365,49 @@
       <c r="AK14" s="7" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="n"/>
-      <c r="B15" s="10" t="n"/>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="10" t="n"/>
-      <c r="E15" s="10" t="n"/>
-      <c r="F15" s="10" t="n"/>
-      <c r="G15" s="10" t="n"/>
-      <c r="H15" s="10" t="n"/>
-      <c r="I15" s="10" t="n"/>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>ESTIMATED TOTAL DUTIES</t>
-        </is>
-      </c>
-      <c r="K15" s="10" t="n"/>
-      <c r="L15" s="10" t="n"/>
-      <c r="M15" s="10" t="n"/>
-      <c r="N15" s="10" t="n"/>
-      <c r="O15" s="10" t="n"/>
-      <c r="P15" s="11" t="n">
-        <v>2529.53</v>
-      </c>
-      <c r="Q15" s="10" t="n"/>
-      <c r="R15" s="10" t="n"/>
-      <c r="S15" s="10" t="n"/>
-      <c r="T15" s="10" t="n"/>
-      <c r="U15" s="10" t="n"/>
-      <c r="V15" s="10" t="n"/>
-      <c r="W15" s="10" t="n"/>
-      <c r="X15" s="10" t="n"/>
-      <c r="Y15" s="10" t="n"/>
-      <c r="Z15" s="10" t="n"/>
-      <c r="AA15" s="10" t="n"/>
-      <c r="AB15" s="10" t="n"/>
-      <c r="AC15" s="10" t="n"/>
-      <c r="AD15" s="10" t="n"/>
-      <c r="AE15" s="10" t="n"/>
-      <c r="AF15" s="10" t="n"/>
-      <c r="AG15" s="10" t="n"/>
-      <c r="AH15" s="10" t="n"/>
-      <c r="AI15" s="10" t="n"/>
-      <c r="AJ15" s="10" t="n"/>
-      <c r="AK15" s="10" t="n"/>
+      <c r="A15" s="7" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="n"/>
+      <c r="I15" s="7" t="n"/>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>CSC (6%)</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="n"/>
+      <c r="L15" s="7" t="n"/>
+      <c r="M15" s="7" t="n"/>
+      <c r="N15" s="7" t="n"/>
+      <c r="O15" s="7" t="n"/>
+      <c r="P15" s="9" t="n">
+        <v>338.02</v>
+      </c>
+      <c r="Q15" s="7" t="n"/>
+      <c r="R15" s="7" t="n"/>
+      <c r="S15" s="7" t="n"/>
+      <c r="T15" s="7" t="n"/>
+      <c r="U15" s="7" t="n"/>
+      <c r="V15" s="7" t="n"/>
+      <c r="W15" s="7" t="n"/>
+      <c r="X15" s="7" t="n"/>
+      <c r="Y15" s="7" t="n"/>
+      <c r="Z15" s="7" t="n"/>
+      <c r="AA15" s="7" t="n"/>
+      <c r="AB15" s="7" t="n"/>
+      <c r="AC15" s="7" t="n"/>
+      <c r="AD15" s="7" t="n"/>
+      <c r="AE15" s="7" t="n"/>
+      <c r="AF15" s="7" t="n"/>
+      <c r="AG15" s="7" t="n"/>
+      <c r="AH15" s="7" t="n"/>
+      <c r="AI15" s="7" t="n"/>
+      <c r="AJ15" s="7" t="n"/>
+      <c r="AK15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n"/>
@@ -1421,7 +1421,7 @@
       <c r="I16" s="7" t="n"/>
       <c r="J16" s="8" t="inlineStr">
         <is>
-          <t>Effective Duty Rate</t>
+          <t>VAT (15%) on CIF+CET+CSC</t>
         </is>
       </c>
       <c r="K16" s="7" t="n"/>
@@ -1429,8 +1429,8 @@
       <c r="M16" s="7" t="n"/>
       <c r="N16" s="7" t="n"/>
       <c r="O16" s="7" t="n"/>
-      <c r="P16" s="12" t="n">
-        <v>0.448998972258068</v>
+      <c r="P16" s="9" t="n">
+        <v>1007.87</v>
       </c>
       <c r="Q16" s="7" t="n"/>
       <c r="R16" s="7" t="n"/>
@@ -1454,6 +1454,96 @@
       <c r="AJ16" s="7" t="n"/>
       <c r="AK16" s="7" t="n"/>
     </row>
+    <row r="17">
+      <c r="A17" s="10" t="n"/>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="10" t="n"/>
+      <c r="G17" s="10" t="n"/>
+      <c r="H17" s="10" t="n"/>
+      <c r="I17" s="10" t="n"/>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>ESTIMATED TOTAL DUTIES</t>
+        </is>
+      </c>
+      <c r="K17" s="10" t="n"/>
+      <c r="L17" s="10" t="n"/>
+      <c r="M17" s="10" t="n"/>
+      <c r="N17" s="10" t="n"/>
+      <c r="O17" s="10" t="n"/>
+      <c r="P17" s="11" t="n">
+        <v>2093.28</v>
+      </c>
+      <c r="Q17" s="10" t="n"/>
+      <c r="R17" s="10" t="n"/>
+      <c r="S17" s="10" t="n"/>
+      <c r="T17" s="10" t="n"/>
+      <c r="U17" s="10" t="n"/>
+      <c r="V17" s="10" t="n"/>
+      <c r="W17" s="10" t="n"/>
+      <c r="X17" s="10" t="n"/>
+      <c r="Y17" s="10" t="n"/>
+      <c r="Z17" s="10" t="n"/>
+      <c r="AA17" s="10" t="n"/>
+      <c r="AB17" s="10" t="n"/>
+      <c r="AC17" s="10" t="n"/>
+      <c r="AD17" s="10" t="n"/>
+      <c r="AE17" s="10" t="n"/>
+      <c r="AF17" s="10" t="n"/>
+      <c r="AG17" s="10" t="n"/>
+      <c r="AH17" s="10" t="n"/>
+      <c r="AI17" s="10" t="n"/>
+      <c r="AJ17" s="10" t="n"/>
+      <c r="AK17" s="10" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="7" t="n"/>
+      <c r="I18" s="7" t="n"/>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>Effective Duty Rate</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="n"/>
+      <c r="L18" s="7" t="n"/>
+      <c r="M18" s="7" t="n"/>
+      <c r="N18" s="7" t="n"/>
+      <c r="O18" s="7" t="n"/>
+      <c r="P18" s="12" t="n">
+        <v>0.3715633215057219</v>
+      </c>
+      <c r="Q18" s="7" t="n"/>
+      <c r="R18" s="7" t="n"/>
+      <c r="S18" s="7" t="n"/>
+      <c r="T18" s="7" t="n"/>
+      <c r="U18" s="7" t="n"/>
+      <c r="V18" s="7" t="n"/>
+      <c r="W18" s="7" t="n"/>
+      <c r="X18" s="7" t="n"/>
+      <c r="Y18" s="7" t="n"/>
+      <c r="Z18" s="7" t="n"/>
+      <c r="AA18" s="7" t="n"/>
+      <c r="AB18" s="7" t="n"/>
+      <c r="AC18" s="7" t="n"/>
+      <c r="AD18" s="7" t="n"/>
+      <c r="AE18" s="7" t="n"/>
+      <c r="AF18" s="7" t="n"/>
+      <c r="AG18" s="7" t="n"/>
+      <c r="AH18" s="7" t="n"/>
+      <c r="AI18" s="7" t="n"/>
+      <c r="AJ18" s="7" t="n"/>
+      <c r="AK18" s="7" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
